--- a/exports/trend_1d/SAGILITY_full_report.xlsx
+++ b/exports/trend_1d/SAGILITY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>18.58</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45681</v>
+        <v>45684</v>
       </c>
       <c r="H2" t="n">
-        <v>47.98</v>
+        <v>45.58</v>
       </c>
       <c r="I2" t="n">
         <v>45.72141019772403</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>37.6</v>
+        <v>30.71</v>
       </c>
       <c r="L2" t="n">
         <v>3.81</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>18.87</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="H3" t="n">
-        <v>50.22</v>
+        <v>52.73</v>
       </c>
       <c r="I3" t="n">
         <v>51.43477736690967</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.18</v>
+        <v>-15.69</v>
       </c>
       <c r="L3" t="n">
-        <v>14.02</v>
+        <v>15.69</v>
       </c>
       <c r="M3" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>-5</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>14.88</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="H4" t="n">
-        <v>45.69</v>
+        <v>44.29</v>
       </c>
       <c r="I4" t="n">
         <v>45.59279231284525</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.35</v>
+        <v>-16.01</v>
       </c>
       <c r="L4" t="n">
-        <v>13.88</v>
+        <v>16.94</v>
       </c>
       <c r="M4" t="n">
         <v>3.9</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.46</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="H5" t="n">
-        <v>42.87</v>
+        <v>45.01</v>
       </c>
       <c r="I5" t="n">
         <v>43.7920360480977</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K5" t="n">
-        <v>3.21</v>
+        <v>-1.63</v>
       </c>
       <c r="L5" t="n">
         <v>3.45</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>12.78</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45803</v>
+        <v>45804</v>
       </c>
       <c r="H6" t="n">
-        <v>42.87</v>
+        <v>40.72</v>
       </c>
       <c r="I6" t="n">
         <v>41.12854729520475</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.75</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>6.22</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>5.02</v>
       </c>
       <c r="N6" t="n">
-        <v>4.56</v>
+        <v>5.02</v>
       </c>
       <c r="O6" t="n">
         <v>4.99</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>14.05</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="H7" t="n">
-        <v>41.16</v>
+        <v>43.72</v>
       </c>
       <c r="I7" t="n">
         <v>43.03107035125253</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.08</v>
+        <v>-7.37</v>
       </c>
       <c r="L7" t="n">
-        <v>5.97</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>1.33</v>
       </c>
       <c r="N7" t="n">
-        <v>4.29</v>
+        <v>6.22</v>
       </c>
       <c r="O7" t="n">
         <v>-5.02</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.37</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H8" t="n">
-        <v>49.69</v>
+        <v>48.47</v>
       </c>
       <c r="I8" t="n">
         <v>48.93055507893592</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K8" t="n">
-        <v>13.66</v>
+        <v>10.86</v>
       </c>
       <c r="L8" t="n">
         <v>7.14</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>15.03</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="H9" t="n">
-        <v>53.41</v>
+        <v>53.84</v>
       </c>
       <c r="I9" t="n">
         <v>53.56651413290668</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.19</v>
+        <v>-11.08</v>
       </c>
       <c r="L9" t="n">
-        <v>11.41</v>
+        <v>12.03</v>
       </c>
       <c r="M9" t="n">
         <v>2.4</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H10" t="n">
-        <v>49.93</v>
+        <v>48.44</v>
       </c>
       <c r="I10" t="n">
         <v>48.93118985183128</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.26</v>
+        <v>-10.03</v>
       </c>
       <c r="L10" t="n">
-        <v>9.970000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6</v>
+        <v>1.86</v>
       </c>
       <c r="N10" t="n">
         <v>4.66</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.18</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H11" t="n">
-        <v>42.82</v>
+        <v>43.16</v>
       </c>
       <c r="I11" t="n">
         <v>42.92462566241618</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K11" t="n">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
       <c r="L11" t="n">
         <v>7.35</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>11.93</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H12" t="n">
-        <v>40.02</v>
+        <v>39</v>
       </c>
       <c r="I12" t="n">
         <v>39.88408833723258</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.28</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>7.81</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>1.19</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>11.12</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="H13" t="n">
-        <v>40.42</v>
+        <v>43.29</v>
       </c>
       <c r="I13" t="n">
         <v>42.75596487358502</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.64</v>
+        <v>-11</v>
       </c>
       <c r="L13" t="n">
-        <v>10.23</v>
+        <v>12.33</v>
       </c>
       <c r="M13" t="n">
         <v>2.52</v>
       </c>
       <c r="N13" t="n">
-        <v>4.34</v>
+        <v>7.1</v>
       </c>
       <c r="O13" t="n">
         <v>-2.55</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.12</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H14" t="n">
-        <v>43.45</v>
+        <v>42.54</v>
       </c>
       <c r="I14" t="n">
         <v>43.11603760884135</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K14" t="n">
-        <v>0.37</v>
+        <v>-1.73</v>
       </c>
       <c r="L14" t="n">
         <v>5.94</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1299,6 +1478,14 @@
       <c r="Q15" t="n">
         <v>20</v>
       </c>
+      <c r="R15" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2245,7 +2432,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.7</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="6">
@@ -2255,7 +2442,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -2265,7 +2452,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
@@ -2275,7 +2462,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2285,7 +2472,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -2295,7 +2482,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="11">
@@ -2335,7 +2522,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.67</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="15">
@@ -2345,7 +2532,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.71</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="16">
@@ -2355,7 +2542,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.71</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="17">
@@ -2365,7 +2552,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37.6</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="18">
@@ -2375,7 +2562,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.5</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="19">
@@ -2385,7 +2572,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.25</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="20">
@@ -2395,7 +2582,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.35</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2405,7 +2592,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.02</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="22">
@@ -2425,7 +2612,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -2435,7 +2622,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.16</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="25">
@@ -2455,7 +2642,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.84</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="27">
@@ -2465,7 +2652,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.89</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="28">
